--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127852823</v>
       </c>
       <c r="B2" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127852823</v>
       </c>
       <c r="B2" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127852823</v>
       </c>
       <c r="B2" t="n">
-        <v>56615</v>
+        <v>56618</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,6 +1370,691 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129141723</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102895</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Edshammar, 1,0 km SSO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>652587</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6652656</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ask- och almsly</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129141861</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106276</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Edshammar, 1,0 km SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>652630</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6652672</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Omkrets i brösthöjd:93 cm</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129141928</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92847</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Edshammar, 920 m SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>652632</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6652719</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129141970</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100839</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Edshammar, 1,0 km SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>652743</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6652722</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129141771</v>
+      </c>
+      <c r="B12" t="n">
+        <v>106276</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Edshammar, 1,0 km SSO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>652602</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6652632</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Omkrets i brösthöjd:1,46 m</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129141711</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106276</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Edshammar, 1,0 km SSO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>652587</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6652656</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lena</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ask- och almsly</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Ängsblandskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102895</v>
+        <v>102900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106276</v>
+        <v>106281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106276</v>
+        <v>106281</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106276</v>
+        <v>106281</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102900</v>
+        <v>102903</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106281</v>
+        <v>106284</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106281</v>
+        <v>106284</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106281</v>
+        <v>106284</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127852823</v>
       </c>
       <c r="B2" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102903</v>
+        <v>102913</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106284</v>
+        <v>106294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106284</v>
+        <v>106294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106284</v>
+        <v>106294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102913</v>
+        <v>102920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106294</v>
+        <v>106301</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106294</v>
+        <v>106301</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106294</v>
+        <v>106301</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102920</v>
+        <v>102922</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106301</v>
+        <v>106303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106301</v>
+        <v>106303</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106301</v>
+        <v>106303</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102922</v>
+        <v>102948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106303</v>
+        <v>106329</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106303</v>
+        <v>106329</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106303</v>
+        <v>106329</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102948</v>
+        <v>102950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106329</v>
+        <v>106331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102950</v>
+        <v>102951</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106331</v>
+        <v>106332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106331</v>
+        <v>106332</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106331</v>
+        <v>106332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102951</v>
+        <v>102955</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106332</v>
+        <v>106336</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106332</v>
+        <v>106336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106332</v>
+        <v>106336</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102955</v>
+        <v>102957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106336</v>
+        <v>106338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100899</v>
+        <v>100901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106336</v>
+        <v>106338</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106336</v>
+        <v>106338</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102957</v>
+        <v>102961</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106338</v>
+        <v>106342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100901</v>
+        <v>100905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106338</v>
+        <v>106342</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106338</v>
+        <v>106342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102961</v>
+        <v>102971</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106342</v>
+        <v>106352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100905</v>
+        <v>100913</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106342</v>
+        <v>106352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106342</v>
+        <v>106352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>129101321</v>
       </c>
       <c r="B3" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         <v>129101350</v>
       </c>
       <c r="B4" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>129112335</v>
       </c>
       <c r="B5" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>129112094</v>
       </c>
       <c r="B6" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129112026</v>
       </c>
       <c r="B7" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102971</v>
+        <v>102974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106352</v>
+        <v>106355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100913</v>
+        <v>100916</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106352</v>
+        <v>106355</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106352</v>
+        <v>106355</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 44601-2025 artfynd.xlsx
+++ b/artfynd/A 44601-2025 artfynd.xlsx
@@ -1375,7 +1375,7 @@
         <v>129141723</v>
       </c>
       <c r="B8" t="n">
-        <v>102974</v>
+        <v>103003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>129141861</v>
       </c>
       <c r="B9" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
         <v>129141928</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>129141970</v>
       </c>
       <c r="B11" t="n">
-        <v>100916</v>
+        <v>100945</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>129141771</v>
       </c>
       <c r="B12" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>129141711</v>
       </c>
       <c r="B13" t="n">
-        <v>106355</v>
+        <v>106384</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
